--- a/Data/EXCEL/Transfer/salemon/20240711/2929-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/2929-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2E99848-DAB1-4690-A768-73591B960CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06C76EB9-1C94-417A-A270-144137404D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4570" yWindow="2620" windowWidth="18240" windowHeight="13390" xr2:uid="{E6611EF2-58D7-476B-A275-A00969BF9C8F}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{1EE7D076-E947-4938-8668-CA0BAA861000}"/>
   </bookViews>
   <sheets>
     <sheet name="2929-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,26 +1261,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83C30A5D-0695-4C0E-A08F-9C9FF384E02C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{550E749D-20FA-4259-940F-B5AD558CED97}">
   <dimension ref="A1:Q268"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1307,7 +1307,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1389,7 +1389,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1428,7 +1428,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>-13.5</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>-12.8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>-14.4</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>-14.4</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>-14.9</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>-6.28</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>-7.99</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>-10.4</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>-13.5</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>-15.8</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>-18.8</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>-21.7</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>-21</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>-20.9</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>-20.100000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>-14.7</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>-13.4</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>-14.1</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>-13.6</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>-12.7</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>-12.6</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>-13.6</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>-14.6</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>-16.100000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>-15.4</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>-14.8</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>-23.9</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>-8.1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>7.68</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>8.08</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3336,7 +3336,7 @@
         <v>8.16</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>6.66</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>-5.53</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>-19.600000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44197</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>-57.8</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>-61.4</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>44136</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>-61.6</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>-61.9</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>44075</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>-62.4</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3919,7 +3919,7 @@
         <v>-59.6</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>44013</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>-58.8</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4025,7 +4025,7 @@
         <v>-55.6</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>43952</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>-50.2</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>-43.4</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>43891</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>-35.6</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>-29.9</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>43831</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>5.98</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>43770</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>43709</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>6.56</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>7.28</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>43647</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>7.17</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4661,7 +4661,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>43586</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>43525</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>8.43</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>9.74</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>43466</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4979,7 +4979,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>43405</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>43344</v>
       </c>
@@ -5138,7 +5138,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5191,7 +5191,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>43282</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5297,7 +5297,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>43221</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>43160</v>
       </c>
@@ -5456,7 +5456,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5509,7 +5509,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>43101</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5615,7 +5615,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>43040</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5721,7 +5721,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>42979</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5827,7 +5827,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>42917</v>
       </c>
@@ -5880,7 +5880,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>42887</v>
       </c>
@@ -5933,7 +5933,7 @@
         <v>-0.99</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>42856</v>
       </c>
@@ -5986,7 +5986,7 @@
         <v>-2.14</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>42826</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>-2.52</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>42795</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>-0.68</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>42767</v>
       </c>
@@ -6145,7 +6145,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>42736</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>42705</v>
       </c>
@@ -6251,7 +6251,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>42675</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>42644</v>
       </c>
@@ -6357,7 +6357,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <v>42614</v>
       </c>
@@ -6410,7 +6410,7 @@
         <v>6.26</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>42583</v>
       </c>
@@ -6463,7 +6463,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="10">
         <v>42552</v>
       </c>
@@ -6516,7 +6516,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>42522</v>
       </c>
@@ -6569,7 +6569,7 @@
         <v>5.79</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="10">
         <v>42491</v>
       </c>
@@ -6622,7 +6622,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>42461</v>
       </c>
@@ -6675,7 +6675,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="10">
         <v>42430</v>
       </c>
@@ -6728,7 +6728,7 @@
         <v>5.96</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>42401</v>
       </c>
@@ -6781,7 +6781,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="10">
         <v>42370</v>
       </c>
@@ -6834,7 +6834,7 @@
         <v>6.18</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>42339</v>
       </c>
@@ -6887,7 +6887,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="10">
         <v>42309</v>
       </c>
@@ -6940,7 +6940,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>42278</v>
       </c>
@@ -6993,7 +6993,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="10">
         <v>42248</v>
       </c>
@@ -7046,7 +7046,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>42217</v>
       </c>
@@ -7099,7 +7099,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="10">
         <v>42186</v>
       </c>
@@ -7152,7 +7152,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>42156</v>
       </c>
@@ -7205,7 +7205,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="10">
         <v>42125</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>42095</v>
       </c>
@@ -7311,7 +7311,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="10">
         <v>42064</v>
       </c>
@@ -7364,7 +7364,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>42036</v>
       </c>
@@ -7417,7 +7417,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>42005</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>41974</v>
       </c>
@@ -7523,7 +7523,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>41944</v>
       </c>
@@ -7576,7 +7576,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>41913</v>
       </c>
@@ -7629,7 +7629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>41883</v>
       </c>
@@ -7682,7 +7682,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>41852</v>
       </c>
@@ -7735,7 +7735,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>41821</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>41791</v>
       </c>
@@ -7841,7 +7841,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="10">
         <v>41760</v>
       </c>
@@ -7894,7 +7894,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>41730</v>
       </c>
@@ -7947,7 +7947,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="10">
         <v>41699</v>
       </c>
@@ -8000,7 +8000,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>41671</v>
       </c>
@@ -8053,7 +8053,7 @@
         <v>47.1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="10">
         <v>41640</v>
       </c>
@@ -8106,7 +8106,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>41609</v>
       </c>
@@ -8159,7 +8159,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="10">
         <v>41579</v>
       </c>
@@ -8212,682 +8212,682 @@
         <v>33.700000000000003</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" s="10">
         <v>44256</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" s="10">
         <v>44197</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" s="10">
         <v>44136</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" s="10">
         <v>44075</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" s="10">
         <v>44013</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" s="10">
         <v>43952</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" s="10">
         <v>43891</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" s="10">
         <v>43831</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A191" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A192" s="10">
         <v>43770</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A193" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A194" s="10">
         <v>43709</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A195" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A196" s="10">
         <v>43647</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A197" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A198" s="10">
         <v>43586</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A199" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A200" s="10">
         <v>43525</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A201" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A202" s="10">
         <v>43466</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A203" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A204" s="10">
         <v>43405</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A205" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A206" s="10">
         <v>43344</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A207" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A208" s="10">
         <v>43282</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A210" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A211" s="10">
         <v>43221</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A212" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A213" s="10">
         <v>43160</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A214" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A215" s="10">
         <v>43101</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A216" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A217" s="10">
         <v>43040</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A218" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A219" s="10">
         <v>42979</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A220" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A221" s="10">
         <v>42917</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A222" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A223" s="10">
         <v>42856</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A224" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A225" s="10">
         <v>42795</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A226" s="5">
         <v>42767</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A227" s="10">
         <v>42736</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A229" s="5">
         <v>42705</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A230" s="10">
         <v>42675</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A231" s="5">
         <v>42644</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A232" s="10">
         <v>42614</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A233" s="5">
         <v>42583</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A234" s="10">
         <v>42552</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A235" s="5">
         <v>42522</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A236" s="10">
         <v>42491</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A237" s="5">
         <v>42461</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A238" s="10">
         <v>42430</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A239" s="5">
         <v>42401</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A240" s="10">
         <v>42370</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A241" s="5">
         <v>42339</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A242" s="10">
         <v>42309</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A243" s="5">
         <v>42278</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A244" s="10">
         <v>42248</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A245" s="5">
         <v>42217</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A246" s="10">
         <v>42186</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A248" s="5">
         <v>42156</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A249" s="10">
         <v>42125</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A250" s="5">
         <v>42095</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A251" s="10">
         <v>42064</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A252" s="5">
         <v>42036</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A253" s="10">
         <v>42005</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A254" s="5">
         <v>41974</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A255" s="10">
         <v>41944</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A256" s="5">
         <v>41913</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A257" s="10">
         <v>41883</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A258" s="5">
         <v>41852</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A259" s="10">
         <v>41821</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A260" s="5">
         <v>41791</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A261" s="10">
         <v>41760</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A262" s="5">
         <v>41730</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A263" s="10">
         <v>41699</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A264" s="5">
         <v>41671</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A265" s="10">
         <v>41640</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A267" s="5">
         <v>41609</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A268" s="10">
         <v>41579</v>
       </c>
